--- a/nse_screener_reference/portfolio_IN_latest.xlsx
+++ b/nse_screener_reference/portfolio_IN_latest.xlsx
@@ -14,8 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Efficient_Frontier" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_MaxSharpe_Weights" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_MinVar_Weights" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_Portfolio_Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISCLAIMER" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_Target_Return_Weights" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_Portfolio_Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DISCLAIMER" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -653,6 +654,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DISCLAIMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>⚠️  Modern Portfolio Theory optimisation on historical returns. Assumes stationarity &amp; normality (false); mean-variance weights overfit the sample. Beta is historical. Educational/research only. NOT investment advice. Consult a SEBI-registered advisor.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1762,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1784,287 +1813,144 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-22.21</v>
+        <v>4.82</v>
       </c>
       <c r="B2" t="n">
-        <v>46.57</v>
+        <v>18.69</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.616</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-18.8</v>
+        <v>6.53</v>
       </c>
       <c r="B3" t="n">
-        <v>34.28</v>
+        <v>16.9</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.738</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-15.4</v>
+        <v>8.23</v>
       </c>
       <c r="B4" t="n">
-        <v>25.15</v>
+        <v>15.51</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.871</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-11.99</v>
+        <v>9.93</v>
       </c>
       <c r="B5" t="n">
-        <v>20.83</v>
+        <v>14.61</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.887</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-8.58</v>
+        <v>11.64</v>
       </c>
       <c r="B6" t="n">
-        <v>18.49</v>
+        <v>14.06</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-5.17</v>
+        <v>13.34</v>
       </c>
       <c r="B7" t="n">
-        <v>17.09</v>
+        <v>13.84</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6830000000000001</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.77</v>
+        <v>15.04</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93</v>
+        <v>13.81</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.519</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.64</v>
+        <v>16.75</v>
       </c>
       <c r="B9" t="n">
-        <v>15.01</v>
+        <v>13.92</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.324</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.05</v>
+        <v>18.45</v>
       </c>
       <c r="B10" t="n">
-        <v>14.34</v>
+        <v>14.21</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.101</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8.460000000000001</v>
+        <v>20.16</v>
       </c>
       <c r="B11" t="n">
-        <v>13.9</v>
+        <v>14.69</v>
       </c>
       <c r="C11" t="n">
-        <v>0.141</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11.86</v>
+        <v>21.86</v>
       </c>
       <c r="B12" t="n">
-        <v>13.7</v>
+        <v>15.43</v>
       </c>
       <c r="C12" t="n">
-        <v>0.392</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15.27</v>
+        <v>23.56</v>
       </c>
       <c r="B13" t="n">
-        <v>13.66</v>
+        <v>19.14</v>
       </c>
       <c r="C13" t="n">
-        <v>0.642</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18.68</v>
+        <v>2.54</v>
       </c>
       <c r="B14" t="n">
-        <v>13.78</v>
+        <v>13.19</v>
       </c>
       <c r="C14" t="n">
-        <v>0.884</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>22.09</v>
-      </c>
-      <c r="B15" t="n">
-        <v>14.06</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.109</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="B16" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.307</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="B17" t="n">
-        <v>15.27</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.467</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>32.31</v>
-      </c>
-      <c r="B18" t="n">
-        <v>16.42</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.572</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>35.72</v>
-      </c>
-      <c r="B19" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.624</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>39.13</v>
-      </c>
-      <c r="B20" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.638</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>42.53</v>
-      </c>
-      <c r="B21" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.629</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>45.94</v>
-      </c>
-      <c r="B22" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.605</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>49.35</v>
-      </c>
-      <c r="B23" t="n">
-        <v>27.31</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.569</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>52.76</v>
-      </c>
-      <c r="B24" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.525</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>56.16</v>
-      </c>
-      <c r="B25" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>59.57</v>
-      </c>
-      <c r="B26" t="n">
-        <v>39.61</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="B27" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="C27" t="n">
         <v>-0.3</v>
       </c>
     </row>
@@ -2079,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,7 +1987,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.06</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2111,27 +1997,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.83</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.08</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -2141,7 +2027,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.380000000000001</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="7">
@@ -2151,27 +2037,47 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.95</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HITECHCORP</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.68</v>
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LGBBROSLTD</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HITECHCORP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.32</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2207,7 +2113,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.82</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2217,47 +2123,47 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>HEIDELBERG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.4</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HEIDELBERG</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.93</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.98</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.97</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="8">
@@ -2267,27 +2173,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.92</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WAAREEINDO</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>WAAREEINDO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.12</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="11">
@@ -2297,7 +2203,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="12">
@@ -2307,7 +2213,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="13">
@@ -2317,7 +2223,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="14">
@@ -2327,7 +2233,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.66</v>
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JKCEMENT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -2341,91 +2257,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Portfolio</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ann_Return%</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Vol%</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sharpe</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Holdings</t>
+          <t>Weight%</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Max-Sharpe (growth fund)</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.638</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Min-Variance (conservative)</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="C3" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="E3" t="n">
-        <v>13</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nifty 50 (benchmark)</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="C4" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>50</v>
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PRIVISCL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11.81</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WAAREEINDO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>JKCEMENT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LGBBROSLTD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RAMCOCEM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.81</v>
       </c>
     </row>
   </sheetData>
@@ -2439,21 +2393,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DISCLAIMER</t>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ann_Return%</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vol%</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Holdings</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚠️  Modern Portfolio Theory optimisation on historical returns. Assumes stationarity &amp; normality (false); mean-variance weights overfit the sample. Beta is historical. Educational/research only. NOT investment advice. Consult a SEBI-registered advisor.</t>
-        </is>
+          <t>Max-Sharpe (growth fund)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Min-Variance (conservative)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Target 20% (min-risk to meet yield)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nifty 50 (benchmark)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
